--- a/分省数据看板（月度）/趋势分析/26年4月.xlsx
+++ b/分省数据看板（月度）/趋势分析/26年4月.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>活跃用户</t>
+  </si>
+  <si>
+    <t>新用户</t>
   </si>
   <si>
     <t>营收</t>
@@ -1112,13 +1115,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="12.625"/>
+    <col min="6" max="6" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1137,684 +1140,789 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1">
         <v>9493</v>
       </c>
       <c r="C2" s="1">
+        <v>4451</v>
+      </c>
+      <c r="D2" s="1">
         <v>48362</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>7013</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>5.09</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>0.7388</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
         <v>8270</v>
       </c>
       <c r="C3" s="1">
+        <v>2929</v>
+      </c>
+      <c r="D3" s="1">
         <v>40385</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>6468</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>4.88</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>0.7821</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
         <v>9128</v>
       </c>
       <c r="C4" s="1">
+        <v>4468</v>
+      </c>
+      <c r="D4" s="1">
         <v>24951</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>6579</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>2.73</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>0.7207</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>4399</v>
       </c>
       <c r="C5" s="1">
+        <v>2494</v>
+      </c>
+      <c r="D5" s="1">
         <v>10389</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>3156</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>2.36</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>0.7174</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>4164</v>
       </c>
       <c r="C6" s="1">
+        <v>1982</v>
+      </c>
+      <c r="D6" s="1">
         <v>16963</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>2966</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>4.07</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>0.7123</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
         <v>12125</v>
       </c>
       <c r="C7" s="1">
+        <v>3727</v>
+      </c>
+      <c r="D7" s="1">
         <v>51479</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>9244</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>4.25</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>0.7624</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1">
         <v>4012</v>
       </c>
       <c r="C8" s="1">
+        <v>1561</v>
+      </c>
+      <c r="D8" s="1">
         <v>16198</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>2969</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>4.04</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>0.74</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1">
         <v>7311</v>
       </c>
       <c r="C9" s="1">
+        <v>2474</v>
+      </c>
+      <c r="D9" s="1">
         <v>29510</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>5453</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>4.04</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>0.7459</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
         <v>4731</v>
       </c>
       <c r="C10" s="1">
+        <v>1954</v>
+      </c>
+      <c r="D10" s="1">
         <v>33475</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>3508</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>7.08</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>0.7415</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1">
         <v>24153</v>
       </c>
       <c r="C11" s="1">
+        <v>9314</v>
+      </c>
+      <c r="D11" s="1">
         <v>136133</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>18240</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>5.64</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>0.7552</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1">
         <v>7693</v>
       </c>
       <c r="C12" s="1">
+        <v>3138</v>
+      </c>
+      <c r="D12" s="1">
         <v>37500</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>5770</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>4.87</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1">
         <v>13135</v>
       </c>
       <c r="C13" s="1">
+        <v>4903</v>
+      </c>
+      <c r="D13" s="1">
         <v>50625</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>9672</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>3.85</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>0.7364</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1">
         <v>11478</v>
       </c>
       <c r="C14" s="1">
+        <v>4285</v>
+      </c>
+      <c r="D14" s="1">
         <v>40761</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>8548</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>3.55</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>0.7447</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>8088</v>
       </c>
       <c r="C15" s="1">
+        <v>3640</v>
+      </c>
+      <c r="D15" s="1">
         <v>15355</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>5833</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>1.9</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>0.7212</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1">
         <v>31960</v>
       </c>
       <c r="C16" s="1">
+        <v>11512</v>
+      </c>
+      <c r="D16" s="1">
         <v>94321</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>25251</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>2.95</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>0.7901</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
         <v>10598</v>
       </c>
       <c r="C17" s="1">
+        <v>5119</v>
+      </c>
+      <c r="D17" s="1">
         <v>20930</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <v>7616</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>1.97</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>0.7186</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>7819</v>
       </c>
       <c r="C18" s="1">
+        <v>3032</v>
+      </c>
+      <c r="D18" s="1">
         <v>26299</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>5707</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>3.36</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>0.7299</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
         <v>9640</v>
       </c>
       <c r="C19" s="1">
+        <v>4114</v>
+      </c>
+      <c r="D19" s="1">
         <v>34399</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>7088</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>3.57</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>0.7353</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1">
         <v>18606</v>
       </c>
       <c r="C20" s="1">
+        <v>7678</v>
+      </c>
+      <c r="D20" s="1">
         <v>72167</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>13676</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>3.88</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>0.735</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1">
         <v>3420</v>
       </c>
       <c r="C21" s="1">
+        <v>1634</v>
+      </c>
+      <c r="D21" s="1">
         <v>9418</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
         <v>2449</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>2.75</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>0.7161</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1">
         <v>1849</v>
       </c>
       <c r="C22" s="1">
+        <v>856</v>
+      </c>
+      <c r="D22" s="1">
         <v>5626</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
         <v>1047</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>3.04</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>0.5663</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1">
         <v>5560</v>
       </c>
       <c r="C23" s="1">
+        <v>2186</v>
+      </c>
+      <c r="D23" s="1">
         <v>27425</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
         <v>4113</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>4.93</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <v>0.7397</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1">
         <v>7822</v>
       </c>
       <c r="C24" s="1">
+        <v>3299</v>
+      </c>
+      <c r="D24" s="1">
         <v>24790</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <v>5766</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>3.17</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <v>0.7372</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1">
         <v>2685</v>
       </c>
       <c r="C25" s="1">
+        <v>1364</v>
+      </c>
+      <c r="D25" s="1">
         <v>5531</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
         <v>1827</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>2.06</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <v>0.6804</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1">
         <v>3208</v>
       </c>
       <c r="C26" s="1">
+        <v>1600</v>
+      </c>
+      <c r="D26" s="1">
         <v>12825</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>2149</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>4</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <v>0.6699</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1">
         <v>203</v>
       </c>
       <c r="C27" s="1">
+        <v>123</v>
+      </c>
+      <c r="D27" s="1">
         <v>1034</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <v>146</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>5.09</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <v>0.7192</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1">
         <v>4669</v>
       </c>
       <c r="C28" s="1">
+        <v>2272</v>
+      </c>
+      <c r="D28" s="1">
         <v>14238</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
         <v>3262</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>3.05</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <v>0.6987</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1">
         <v>3459</v>
       </c>
       <c r="C29" s="1">
+        <v>1658</v>
+      </c>
+      <c r="D29" s="1">
         <v>6611</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
         <v>2501</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>1.91</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <v>0.723</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1">
         <v>811</v>
       </c>
       <c r="C30" s="1">
+        <v>369</v>
+      </c>
+      <c r="D30" s="1">
         <v>2528</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <v>600</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <v>3.12</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>0.7398</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1">
         <v>1430</v>
       </c>
       <c r="C31" s="1">
+        <v>642</v>
+      </c>
+      <c r="D31" s="1">
         <v>4010</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>1078</v>
       </c>
-      <c r="E31" s="1">
+      <c r="F31" s="1">
         <v>2.8</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <v>0.7538</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1">
         <v>4109</v>
       </c>
       <c r="C32" s="1">
+        <v>1977</v>
+      </c>
+      <c r="D32" s="1">
         <v>11561</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <v>2787</v>
       </c>
-      <c r="E32" s="1">
+      <c r="F32" s="1">
         <v>2.81</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <v>0.6783</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1">
         <v>15</v>
       </c>
       <c r="C33" s="1">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1">
         <v>49</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <v>11</v>
       </c>
-      <c r="E33" s="1">
+      <c r="F33" s="1">
         <v>3.27</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <v>0.7333</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1">
         <v>5</v>
       </c>
       <c r="C34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1">
         <v>49</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>4</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <v>9.8</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1">
         <v>0</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>0</v>
       </c>
       <c r="D35" s="3">
         <v>0</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="3">
         <v>0</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
         <v>0</v>
       </c>
     </row>
